--- a/results/2019_gnn.xlsx
+++ b/results/2019_gnn.xlsx
@@ -534,28 +534,28 @@
         <v>0.2</v>
       </c>
       <c r="D2" t="n">
-        <v>0.481</v>
+        <v>0.484</v>
       </c>
       <c r="E2" t="n">
-        <v>0.718</v>
+        <v>0.719</v>
       </c>
       <c r="F2" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="G2" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.097</v>
+        <v>0.218</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.098</v>
       </c>
       <c r="I2" t="n">
-        <v>0.236</v>
+        <v>0.237</v>
       </c>
       <c r="J2" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="K2" t="n">
-        <v>0.515</v>
+        <v>0.517</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -577,31 +577,31 @@
         <v>0.042</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.251</v>
+        <v>0.246</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.514</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.736</v>
+        <v>0.737</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="G3" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.099</v>
+        <v>0.195</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.097</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.367</v>
+        <v>0.365</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.552</v>
+        <v>0.551</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -1352,31 +1352,31 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.089</v>
+        <v>0.083</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="E14" s="3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>0.597</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.695</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.759</v>
+        <v>0.767</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.139</v>
+        <v>0.135</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.275</v>
+        <v>0.278</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.368</v>
+        <v>0.373</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.532</v>
+        <v>0.539</v>
       </c>
       <c r="L14" s="4" t="n">
         <v>0</v>
@@ -1405,31 +1405,31 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.031</v>
+        <v>0.027</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0.6</v>
+        <v>0.158</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.585</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.82</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.82</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.244</v>
+        <v>0.228</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.361</v>
+        <v>0.348</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.576</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q95"/>
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1983,34 +1983,34 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0.444</v>
+        <v>0.04</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.24</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.778</v>
+        <v>0.6</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.889</v>
+        <v>0.76</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.927</v>
+        <v>0.82</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.447</v>
+        <v>0.18</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>0.301</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.583</v>
+        <v>0.408</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.768</v>
+        <v>0.586</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>ICD10_C18</t>
+          <t>ICD10_C16</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -2043,35 +2043,35 @@
           <t>sage</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0.556</v>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.04</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.667</v>
+        <v>0.48</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.889</v>
+        <v>0.76</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.874</v>
+        <v>0.784</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>0.462</v>
+        <v>0.217</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.122</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.551</v>
+        <v>0.255</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.697</v>
+        <v>0.509</v>
       </c>
       <c r="M3" s="4" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>ICD10_C18</t>
+          <t>ICD10_C16</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -2105,34 +2105,34 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.397</v>
+        <v>0.111</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.927</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>0</v>
+        <v>0.074</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0.197</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>0.036</v>
+        <v>0.447</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>0.768</v>
       </c>
       <c r="M4" s="6" t="n">
         <v>0</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>ICD10_C23</t>
+          <t>ICD10_C18</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr">
@@ -2166,34 +2166,34 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>1</v>
+        <v>0.556</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.667</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>0.912</v>
+        <v>0.889</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.874</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.126</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0.627</v>
+        <v>0.462</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.697</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>ICD10_C23</t>
+          <t>ICD10_C18</t>
         </is>
       </c>
       <c r="Q5" s="5" t="inlineStr">
@@ -2232,29 +2232,29 @@
       <c r="D6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.906</v>
+        <v>0.397</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="I6" s="3" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.219</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.604</v>
+        <v>0.036</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>ICD10_C43</t>
+          <t>ICD10_C23</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -2300,22 +2300,22 @@
         <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.979</v>
+        <v>0.912</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.021</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.504</v>
+        <v>0.06</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.71</v>
+        <v>0.244</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.893</v>
+        <v>0.627</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>ICD10_C43</t>
+          <t>ICD10_C23</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -2355,28 +2355,28 @@
         <v>0</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.049</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.23</v>
+        <v>1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.48</v>
+        <v>0.906</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>0.134</v>
+        <v>0.094</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0.604</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>0</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>ICD10_C50</t>
+          <t>ICD10_C43</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr">
@@ -2415,29 +2415,29 @@
       <c r="D9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0.164</v>
+      <c r="E9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.492</v>
+        <v>0.979</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.508</v>
+        <v>0.021</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>0.117</v>
+        <v>0.032</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0.893</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="P9" s="5" t="inlineStr">
         <is>
-          <t>ICD10_C50</t>
+          <t>ICD10_C43</t>
         </is>
       </c>
       <c r="Q9" s="5" t="inlineStr">
@@ -2477,28 +2477,28 @@
         <v>0</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.667</v>
+        <v>0.049</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0.872</v>
+        <v>0.23</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.48</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.128</v>
+        <v>0.52</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.123</v>
+        <v>0.015</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.288</v>
+        <v>0.032</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.578</v>
+        <v>0.134</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>ICD10_C53</t>
+          <t>ICD10_C50</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2538,28 +2538,28 @@
         <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.82</v>
+        <v>0.016</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.492</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.18</v>
+        <v>0.508</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.183</v>
+        <v>0.013</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.443</v>
+        <v>0.117</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>ICD10_C53</t>
+          <t>ICD10_C50</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2593,34 +2593,34 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0.263</v>
+        <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0.743</v>
+        <v>1</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.872</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.258</v>
+        <v>0.128</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.553</v>
+        <v>0.123</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.604</v>
+        <v>0.288</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.657</v>
+        <v>0.578</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="P12" s="5" t="inlineStr">
         <is>
-          <t>ICD10_C67</t>
+          <t>ICD10_C53</t>
         </is>
       </c>
       <c r="Q12" s="5" t="inlineStr">
@@ -2653,35 +2653,35 @@
           <t>sage</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>0.6840000000000001</v>
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.333</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>0.762</v>
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.82</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>0.203</v>
+        <v>0.18</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.419</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.513</v>
+        <v>0.183</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.627</v>
+        <v>0.443</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>0</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
-          <t>ICD10_C67</t>
+          <t>ICD10_C53</t>
         </is>
       </c>
       <c r="Q13" s="5" t="inlineStr">
@@ -2715,34 +2715,34 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.25</v>
+        <v>0.263</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.75</v>
+        <v>0.579</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0.989</v>
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.743</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.011</v>
+        <v>0.258</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.385</v>
+        <v>0.39</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.735</v>
+        <v>0.553</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.85</v>
+        <v>0.604</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.946</v>
+        <v>0.657</v>
       </c>
       <c r="M14" s="4" t="n">
         <v>0</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>ICD10_C81</t>
+          <t>ICD10_C67</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -2776,31 +2776,31 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.5</v>
+        <v>0.421</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.6840000000000001</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0.904</v>
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.762</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.096</v>
+        <v>0.239</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.014</v>
+        <v>0.203</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.17</v>
+        <v>0.419</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.315</v>
+        <v>0.513</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>0.627</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>ICD10_C81</t>
+          <t>ICD10_C67</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.75</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>1</v>
@@ -2848,23 +2848,23 @@
       <c r="F16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>0.967</v>
+      <c r="G16" s="6" t="n">
+        <v>0.989</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0.84</v>
+        <v>0.011</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>0.946</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>0</v>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="P16" s="5" t="inlineStr">
         <is>
-          <t>ICD10_D57</t>
+          <t>ICD10_C81</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the blood and blood-forming organs and certain disorders involving the immune mechanism</t>
+          <t>Neoplasms</t>
         </is>
       </c>
     </row>
@@ -2897,35 +2897,35 @@
           <t>sage</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>1</v>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="6" t="n">
-        <v>0.99</v>
+      <c r="G17" s="5" t="n">
+        <v>0.904</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>0.854</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0.949</v>
+        <v>0.096</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0.627</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>0</v>
@@ -2938,12 +2938,12 @@
       </c>
       <c r="P17" s="5" t="inlineStr">
         <is>
-          <t>ICD10_D57</t>
+          <t>ICD10_C81</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the blood and blood-forming organs and certain disorders involving the immune mechanism</t>
+          <t>Neoplasms</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       <c r="C18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="4" t="n">
@@ -2971,22 +2971,22 @@
         <v>1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.969</v>
+        <v>0.967</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.368</v>
+        <v>0.348</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.607</v>
+        <v>0.59</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.848</v>
+        <v>0.84</v>
       </c>
       <c r="M18" s="4" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>ICD10_D66</t>
+          <t>ICD10_D57</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>1</v>
@@ -3032,22 +3032,22 @@
         <v>1</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.974</v>
+        <v>0.99</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.026</v>
+        <v>0.01</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.016</v>
+        <v>0.208</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.439</v>
+        <v>0.73</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.662</v>
+        <v>0.854</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.872</v>
+        <v>0.949</v>
       </c>
       <c r="M19" s="4" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>ICD10_D66</t>
+          <t>ICD10_D57</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -3087,28 +3087,28 @@
         <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0.708</v>
+        <v>1</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.969</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>0</v>
+        <v>0.031</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0.368</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L20" s="6" t="n">
-        <v>0.213</v>
+        <v>0.607</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0.848</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="P20" s="5" t="inlineStr">
         <is>
-          <t>ICD10_D83</t>
+          <t>ICD10_D66</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr">
@@ -3148,28 +3148,28 @@
         <v>0</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0.657</v>
+        <v>1</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.974</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.343</v>
+        <v>0.026</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0</v>
+        <v>0.439</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>0.19</v>
+        <v>0.662</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>0.872</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="P21" s="5" t="inlineStr">
         <is>
-          <t>ICD10_D83</t>
+          <t>ICD10_D66</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr">
@@ -3203,34 +3203,34 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0.857</v>
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0.958</v>
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0.708</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.043</v>
+        <v>0.292</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.546</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>0.828</v>
+        <v>0.011</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0.213</v>
       </c>
       <c r="M22" s="4" t="n">
         <v>0</v>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>ICD10_E11</t>
+          <t>ICD10_D83</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>Endocrine, nutritional and metabolic diseases</t>
+          <t>Diseases of the blood and blood-forming organs and certain disorders involving the immune mechanism</t>
         </is>
       </c>
     </row>
@@ -3263,35 +3263,35 @@
           <t>sage</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0.971</v>
+        <v>0.5</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.657</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>0.482</v>
+        <v>0.343</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>0.863</v>
+        <v>0.013</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0.19</v>
       </c>
       <c r="M23" s="4" t="n">
         <v>0</v>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>ICD10_E11</t>
+          <t>ICD10_D83</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>Endocrine, nutritional and metabolic diseases</t>
+          <t>Diseases of the blood and blood-forming organs and certain disorders involving the immune mechanism</t>
         </is>
       </c>
     </row>
@@ -3325,34 +3325,34 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0.2</v>
+        <v>0.571</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.857</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0.53</v>
+        <v>1</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.958</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.47</v>
+        <v>0.043</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>0.225</v>
+        <v>0.546</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0.828</v>
       </c>
       <c r="M24" s="6" t="n">
         <v>0</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="P24" s="5" t="inlineStr">
         <is>
-          <t>ICD10_E66</t>
+          <t>ICD10_E11</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
@@ -3385,35 +3385,35 @@
           <t>sage</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>0.571</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0.519</v>
+        <v>1</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.971</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>0.029</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>0.13</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>0.196</v>
+        <v>0.482</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0.863</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="P25" s="5" t="inlineStr">
         <is>
-          <t>ICD10_E66</t>
+          <t>ICD10_E11</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
@@ -3449,32 +3449,32 @@
       <c r="C26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0.513</v>
+        <v>0.2</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.53</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>0.19</v>
+        <v>0.47</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>0.225</v>
       </c>
       <c r="M26" s="4" t="n">
         <v>0</v>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>ICD10_F01</t>
+          <t>ICD10_E66</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>Mental and behavioural disorders</t>
+          <t>Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
@@ -3511,31 +3511,31 @@
         <v>0</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>0.107</v>
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0.544</v>
+        <v>0.4</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.519</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.456</v>
+        <v>0.481</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>0.208</v>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.196</v>
       </c>
       <c r="M27" s="4" t="n">
         <v>0</v>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>ICD10_F01</t>
+          <t>ICD10_E66</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>Mental and behavioural disorders</t>
+          <t>Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
@@ -3571,32 +3571,32 @@
       <c r="C28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>0.653</v>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.513</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="I28" s="6" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="I28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0.002</v>
+        <v>0.024</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>0.245</v>
+        <v>0.06</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0.19</v>
       </c>
       <c r="M28" s="6" t="n">
         <v>0</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="P28" s="5" t="inlineStr">
         <is>
-          <t>ICD10_F20</t>
+          <t>ICD10_F01</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
@@ -3633,31 +3633,31 @@
         <v>0</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.601</v>
+        <v>0.107</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0.544</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.399</v>
+        <v>0.456</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.022</v>
+        <v>0.043</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>0.215</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>0.208</v>
       </c>
       <c r="M29" s="6" t="n">
         <v>0</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="P29" s="5" t="inlineStr">
         <is>
-          <t>ICD10_F20</t>
+          <t>ICD10_F01</t>
         </is>
       </c>
       <c r="Q29" s="5" t="inlineStr">
@@ -3696,29 +3696,29 @@
       <c r="D30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.615</v>
+        <v>0.653</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.385</v>
+        <v>0.347</v>
       </c>
       <c r="I30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="4" t="n">
+      <c r="J30" s="3" t="n">
         <v>0.002</v>
       </c>
+      <c r="K30" s="3" t="n">
+        <v>0.033</v>
+      </c>
       <c r="L30" s="4" t="n">
-        <v>0.125</v>
+        <v>0.245</v>
       </c>
       <c r="M30" s="4" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>ICD10_F31</t>
+          <t>ICD10_F20</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -3758,28 +3758,28 @@
         <v>0</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>0</v>
+        <v>0.125</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.375</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.611</v>
+        <v>0.601</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.389</v>
+        <v>0.399</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.002</v>
+        <v>0.062</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.123</v>
+        <v>0.215</v>
       </c>
       <c r="M31" s="4" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>ICD10_F31</t>
+          <t>ICD10_F20</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3813,34 +3813,34 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.78</v>
+        <v>0.615</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.22</v>
+        <v>0.385</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.141</v>
+        <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0.504</v>
+        <v>0</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>0.125</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>0</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="P32" s="5" t="inlineStr">
         <is>
-          <t>ICD10_F72</t>
+          <t>ICD10_F31</t>
         </is>
       </c>
       <c r="Q32" s="5" t="inlineStr">
@@ -3873,35 +3873,35 @@
           <t>sage</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0.2</v>
+      <c r="C33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>0.6</v>
+        <v>0</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.717</v>
+        <v>0.611</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>0.239</v>
+        <v>0.389</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="L33" s="6" t="n">
-        <v>0.506</v>
+        <v>0.002</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0.123</v>
       </c>
       <c r="M33" s="6" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="P33" s="5" t="inlineStr">
         <is>
-          <t>ICD10_F72</t>
+          <t>ICD10_F31</t>
         </is>
       </c>
       <c r="Q33" s="5" t="inlineStr">
@@ -3935,34 +3935,34 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>0.429</v>
+        <v>0.1</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>0.752</v>
+        <v>0.7</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0.78</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0.061</v>
+        <v>0.22</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>0.269</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>0.438</v>
+        <v>0.343</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.504</v>
       </c>
       <c r="M34" s="4" t="n">
         <v>0</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>ICD10_F90</t>
+          <t>ICD10_F72</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3995,35 +3995,35 @@
           <t>sage</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>0.286</v>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>0.778</v>
+        <v>0.6</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.717</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>0.112</v>
+        <v>0.283</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0.239</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>0.415</v>
+        <v>0.352</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0.506</v>
       </c>
       <c r="M35" s="4" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>ICD10_F90</t>
+          <t>ICD10_F72</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -4062,29 +4062,29 @@
       <c r="D36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="5" t="n">
-        <v>0</v>
+      <c r="E36" s="6" t="n">
+        <v>0.429</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.893</v>
+        <v>0.752</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.107</v>
+        <v>0.248</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0.032</v>
+        <v>0.061</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.174</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>0.438</v>
       </c>
       <c r="M36" s="6" t="n">
         <v>0</v>
@@ -4097,12 +4097,12 @@
       </c>
       <c r="P36" s="5" t="inlineStr">
         <is>
-          <t>ICD10_G10</t>
+          <t>ICD10_F90</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the nervous system</t>
+          <t>Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
@@ -4121,31 +4121,31 @@
         <v>0</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>1</v>
+        <v>0.143</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.571</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.995</v>
+        <v>0.778</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.005</v>
+        <v>0.222</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.458</v>
+        <v>0.02</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0.855</v>
+        <v>0.112</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="L37" s="6" t="n">
-        <v>0.974</v>
+        <v>0.192</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>0.415</v>
       </c>
       <c r="M37" s="6" t="n">
         <v>0</v>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="P37" s="5" t="inlineStr">
         <is>
-          <t>ICD10_G10</t>
+          <t>ICD10_F90</t>
         </is>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the nervous system</t>
+          <t>Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
@@ -4181,32 +4181,32 @@
       <c r="C38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="4" t="n">
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.508</v>
+        <v>0.893</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v>0.131</v>
+        <v>0.107</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0.5639999999999999</v>
       </c>
       <c r="M38" s="4" t="n">
         <v>0</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>ICD10_G20</t>
+          <t>ICD10_G10</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -4243,31 +4243,31 @@
         <v>0</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0.581</v>
+        <v>0.995</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.419</v>
+        <v>0.005</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0</v>
+        <v>0.458</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>0.114</v>
+        <v>0.855</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0.974</v>
       </c>
       <c r="M39" s="4" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>ICD10_G20</t>
+          <t>ICD10_G10</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>0.508</v>
@@ -4321,14 +4321,14 @@
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>0.136</v>
+      <c r="J40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="L40" s="6" t="n">
+        <v>0.131</v>
       </c>
       <c r="M40" s="6" t="n">
         <v>0</v>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="P40" s="5" t="inlineStr">
         <is>
-          <t>ICD10_G24</t>
+          <t>ICD10_G20</t>
         </is>
       </c>
       <c r="Q40" s="5" t="inlineStr">
@@ -4370,26 +4370,26 @@
       <c r="E41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="6" t="n">
-        <v>0.25</v>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.623</v>
+        <v>0.581</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.377</v>
+        <v>0.419</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="L41" s="6" t="n">
-        <v>0.206</v>
+        <v>0</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0.114</v>
       </c>
       <c r="M41" s="6" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="P41" s="5" t="inlineStr">
         <is>
-          <t>ICD10_G24</t>
+          <t>ICD10_G20</t>
         </is>
       </c>
       <c r="Q41" s="5" t="inlineStr">
@@ -4429,28 +4429,28 @@
         <v>0</v>
       </c>
       <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>0.375</v>
-      </c>
       <c r="G42" s="3" t="n">
-        <v>0.591</v>
+        <v>0.508</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.409</v>
+        <v>0.492</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>0.173</v>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0.011</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.304</v>
+        <v>0.136</v>
       </c>
       <c r="M42" s="4" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>ICD10_G30</t>
+          <t>ICD10_G24</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4490,28 +4490,28 @@
         <v>0</v>
       </c>
       <c r="E43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>0.5</v>
-      </c>
       <c r="G43" s="4" t="n">
-        <v>0.664</v>
+        <v>0.623</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0.116</v>
+        <v>0.377</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0.041</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.32</v>
+        <v>0.206</v>
       </c>
       <c r="M43" s="4" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>ICD10_G30</t>
+          <t>ICD10_G24</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -4551,28 +4551,28 @@
         <v>0</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>0.882</v>
+        <v>0.25</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.591</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="L44" s="6" t="n">
-        <v>0.598</v>
+        <v>0.409</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0.304</v>
       </c>
       <c r="M44" s="6" t="n">
         <v>0</v>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="P44" s="5" t="inlineStr">
         <is>
-          <t>ICD10_G40</t>
+          <t>ICD10_G30</t>
         </is>
       </c>
       <c r="Q44" s="5" t="inlineStr">
@@ -4612,28 +4612,28 @@
         <v>0</v>
       </c>
       <c r="E45" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F45" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="F45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.861</v>
+      <c r="G45" s="6" t="n">
+        <v>0.664</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>0.571</v>
+        <v>0.336</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>0.32</v>
       </c>
       <c r="M45" s="6" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="P45" s="5" t="inlineStr">
         <is>
-          <t>ICD10_G40</t>
+          <t>ICD10_G30</t>
         </is>
       </c>
       <c r="Q45" s="5" t="inlineStr">
@@ -4672,29 +4672,29 @@
       <c r="D46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0.694</v>
+      <c r="E46" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0.882</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.306</v>
+        <v>0.118</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.02</v>
+        <v>0.222</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>0.337</v>
+        <v>0.349</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>0.598</v>
       </c>
       <c r="M46" s="4" t="n">
         <v>0</v>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>ICD10_G43</t>
+          <t>ICD10_G40</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -4739,23 +4739,23 @@
       <c r="F47" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="4" t="n">
-        <v>0.854</v>
+      <c r="G47" s="3" t="n">
+        <v>0.861</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.146</v>
+        <v>0.139</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>0.002</v>
+        <v>0.013</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>0.519</v>
+        <v>0.354</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>0.571</v>
       </c>
       <c r="M47" s="4" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>ICD10_G43</t>
+          <t>ICD10_G40</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -4795,28 +4795,28 @@
         <v>0</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>0.734</v>
+        <v>0.25</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.694</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="I48" s="6" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="I48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>0.007</v>
+        <v>0.02</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>0.06</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>0.305</v>
+        <v>0.337</v>
       </c>
       <c r="M48" s="6" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="P48" s="5" t="inlineStr">
         <is>
-          <t>ICD10_G91</t>
+          <t>ICD10_G43</t>
         </is>
       </c>
       <c r="Q48" s="5" t="inlineStr">
@@ -4859,25 +4859,25 @@
         <v>0.5</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0.854</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.31</v>
+        <v>0.146</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.238</v>
+        <v>0.229</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.412</v>
+        <v>0.519</v>
       </c>
       <c r="M49" s="6" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="P49" s="5" t="inlineStr">
         <is>
-          <t>ICD10_G91</t>
+          <t>ICD10_G43</t>
         </is>
       </c>
       <c r="Q49" s="5" t="inlineStr">
@@ -4914,31 +4914,31 @@
         <v>0</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>0.824</v>
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0.734</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.176</v>
+        <v>0.266</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>0.569</v>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.305</v>
       </c>
       <c r="M50" s="4" t="n">
         <v>0</v>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>ICD10_I10</t>
+          <t>ICD10_G91</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the circulatory system</t>
+          <t>Diseases of the nervous system</t>
         </is>
       </c>
     </row>
@@ -4974,32 +4974,32 @@
       <c r="C51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="3" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>0.333</v>
+      <c r="D51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0.5</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>0.837</v>
+        <v>0.5</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="J51" s="3" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>0.475</v>
+        <v>0.31</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>0.412</v>
       </c>
       <c r="M51" s="4" t="n">
         <v>0</v>
@@ -5012,12 +5012,12 @@
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>ICD10_I10</t>
+          <t>ICD10_G91</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the circulatory system</t>
+          <t>Diseases of the nervous system</t>
         </is>
       </c>
     </row>
@@ -5035,32 +5035,32 @@
       <c r="C52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>0.28</v>
+      <c r="D52" s="6" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>0.467</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.718</v>
+        <v>0.824</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>0.399</v>
+        <v>0.176</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="L52" s="6" t="n">
+        <v>0.569</v>
       </c>
       <c r="M52" s="6" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="P52" s="5" t="inlineStr">
         <is>
-          <t>ICD10_I25</t>
+          <t>ICD10_I10</t>
         </is>
       </c>
       <c r="Q52" s="5" t="inlineStr">
@@ -5096,32 +5096,32 @@
       <c r="C53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E53" s="6" t="n">
-        <v>0.32</v>
+      <c r="D53" s="5" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.333</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0.72</v>
+        <v>0.867</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0.756</v>
+        <v>0.837</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="K53" s="6" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="L53" s="6" t="n">
-        <v>0.462</v>
+        <v>0.164</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.475</v>
       </c>
       <c r="M53" s="6" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P53" s="5" t="inlineStr">
         <is>
-          <t>ICD10_I25</t>
+          <t>ICD10_I10</t>
         </is>
       </c>
       <c r="Q53" s="5" t="inlineStr">
@@ -5157,32 +5157,32 @@
       <c r="C54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>0</v>
+      <c r="D54" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.28</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.52</v>
+        <v>0.718</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>0</v>
+        <v>0.282</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>0.033</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.074</v>
+        <v>0.399</v>
       </c>
       <c r="M54" s="4" t="n">
         <v>0</v>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>ICD10_I26</t>
+          <t>ICD10_I25</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -5219,31 +5219,31 @@
         <v>0</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>0.806</v>
+        <v>0.756</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.194</v>
+        <v>0.244</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>0.002</v>
+        <v>0.181</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0.044</v>
+        <v>0.257</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>0.354</v>
+        <v>0.462</v>
       </c>
       <c r="M55" s="4" t="n">
         <v>0</v>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>ICD10_I26</t>
+          <t>ICD10_I25</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -5276,36 +5276,36 @@
           <t>gcn</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.736</v>
+        <v>0.52</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="I56" s="5" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="L56" s="6" t="n">
         <v>0.48</v>
       </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0.074</v>
+      </c>
       <c r="M56" s="6" t="n">
         <v>0</v>
       </c>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P56" s="5" t="inlineStr">
         <is>
-          <t>ICD10_I42</t>
+          <t>ICD10_I26</t>
         </is>
       </c>
       <c r="Q56" s="5" t="inlineStr">
@@ -5338,34 +5338,34 @@
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0.333</v>
+        <v>0</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0.778</v>
+        <v>1</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.783</v>
+        <v>0.806</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.217</v>
+        <v>0.194</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="J57" s="5" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="K57" s="5" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>0.476</v>
+        <v>0</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>0.354</v>
       </c>
       <c r="M57" s="6" t="n">
         <v>0</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P57" s="5" t="inlineStr">
         <is>
-          <t>ICD10_I42</t>
+          <t>ICD10_I26</t>
         </is>
       </c>
       <c r="Q57" s="5" t="inlineStr">
@@ -5398,35 +5398,35 @@
           <t>gcn</t>
         </is>
       </c>
-      <c r="C58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>0.115</v>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>0.111</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>0.723</v>
+        <v>0.444</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0.736</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="J58" s="3" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="K58" s="3" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="L58" s="3" t="n">
-        <v>0.408</v>
+        <v>0.265</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>0.48</v>
       </c>
       <c r="M58" s="4" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>ICD10_I50</t>
+          <t>ICD10_I42</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -5460,34 +5460,34 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>0.154</v>
+        <v>0.111</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0.269</v>
+        <v>0.333</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>0.718</v>
+        <v>0.778</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0.783</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="I59" s="3" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="J59" s="4" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="K59" s="4" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="L59" s="4" t="n">
-        <v>0.41</v>
+        <v>0.217</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>0.476</v>
       </c>
       <c r="M59" s="4" t="n">
         <v>0</v>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>ICD10_I50</t>
+          <t>ICD10_I42</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -5523,32 +5523,32 @@
       <c r="C60" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="6" t="n">
-        <v>0.5</v>
+      <c r="D60" s="5" t="n">
+        <v>0.115</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>0.5</v>
+        <v>0.308</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0.901</v>
+        <v>0.654</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>0.723</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>0.116</v>
+        <v>0.278</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>0.044</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>0.374</v>
+        <v>0.132</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0.455</v>
+        <v>0.206</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0.658</v>
+        <v>0.408</v>
       </c>
       <c r="M60" s="6" t="n">
         <v>0</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="P60" s="5" t="inlineStr">
         <is>
-          <t>ICD10_I63</t>
+          <t>ICD10_I50</t>
         </is>
       </c>
       <c r="Q60" s="5" t="inlineStr">
@@ -5585,31 +5585,31 @@
         <v>0</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>0.5</v>
+        <v>0.154</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0.269</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.654</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.718</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="I61" s="6" t="n">
-        <v>0.152</v>
+        <v>0.283</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>0.038</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.409</v>
+        <v>0.143</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>0.53</v>
+        <v>0.215</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>0.759</v>
+        <v>0.41</v>
       </c>
       <c r="M61" s="6" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="P61" s="5" t="inlineStr">
         <is>
-          <t>ICD10_I63</t>
+          <t>ICD10_I50</t>
         </is>
       </c>
       <c r="Q61" s="5" t="inlineStr">
@@ -5642,35 +5642,35 @@
           <t>gcn</t>
         </is>
       </c>
-      <c r="C62" s="3" t="n">
-        <v>0.333</v>
+      <c r="C62" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="4" t="n">
-        <v>0.97</v>
+      <c r="G62" s="3" t="n">
+        <v>0.901</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.031</v>
+        <v>0.1</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.391</v>
+        <v>0.116</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.61</v>
+        <v>0.374</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.712</v>
-      </c>
-      <c r="L62" s="4" t="n">
-        <v>0.866</v>
+        <v>0.455</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>0.658</v>
       </c>
       <c r="M62" s="4" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>ICD10_I70</t>
+          <t>ICD10_I63</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -5704,34 +5704,34 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>0.5</v>
       </c>
       <c r="F63" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="3" t="n">
-        <v>0.964</v>
+      <c r="G63" s="4" t="n">
+        <v>0.9419999999999999</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.036</v>
+        <v>0.059</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.152</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>0.655</v>
+        <v>0.409</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>0.852</v>
+        <v>0.53</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>0.759</v>
       </c>
       <c r="M63" s="4" t="n">
         <v>0</v>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>ICD10_I70</t>
+          <t>ICD10_I63</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -5764,11 +5764,11 @@
           <t>gcn</t>
         </is>
       </c>
-      <c r="C64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>0</v>
+      <c r="C64" s="5" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>0.667</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>1</v>
@@ -5776,23 +5776,23 @@
       <c r="F64" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="5" t="n">
-        <v>0.9350000000000001</v>
+      <c r="G64" s="6" t="n">
+        <v>0.97</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0.065</v>
+        <v>0.031</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>0</v>
+        <v>0.391</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>0.123</v>
+        <v>0.61</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>0.707</v>
+        <v>0.712</v>
+      </c>
+      <c r="L64" s="6" t="n">
+        <v>0.866</v>
       </c>
       <c r="M64" s="6" t="n">
         <v>0</v>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="P64" s="5" t="inlineStr">
         <is>
-          <t>ICD10_J45</t>
+          <t>ICD10_I70</t>
         </is>
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the respiratory system</t>
+          <t>Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
@@ -5826,34 +5826,34 @@
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="6" t="n">
-        <v>1</v>
+        <v>0.667</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0.667</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G65" s="6" t="n">
-        <v>0.994</v>
+      <c r="G65" s="5" t="n">
+        <v>0.964</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.006</v>
+        <v>0.036</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>0.362</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>0.903</v>
-      </c>
-      <c r="L65" s="6" t="n">
-        <v>0.967</v>
+        <v>0.716</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>0.852</v>
       </c>
       <c r="M65" s="6" t="n">
         <v>0</v>
@@ -5866,12 +5866,12 @@
       </c>
       <c r="P65" s="5" t="inlineStr">
         <is>
-          <t>ICD10_J45</t>
+          <t>ICD10_I70</t>
         </is>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the respiratory system</t>
+          <t>Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
@@ -5889,32 +5889,32 @@
       <c r="C66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>0.667</v>
+        <v>1</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.879</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="I66" s="4" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="J66" s="4" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="K66" s="4" t="n">
-        <v>0.478</v>
-      </c>
-      <c r="L66" s="4" t="n">
-        <v>0.656</v>
+        <v>0.065</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0.707</v>
       </c>
       <c r="M66" s="4" t="n">
         <v>0</v>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>ICD10_J62</t>
+          <t>ICD10_J45</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -5951,31 +5951,31 @@
         <v>0</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="F67" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>0.898</v>
+        <v>0.994</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="K67" s="3" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="L67" s="3" t="n">
-        <v>0.601</v>
+        <v>0.006</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="J67" s="4" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>0.967</v>
       </c>
       <c r="M67" s="4" t="n">
         <v>0</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>ICD10_J62</t>
+          <t>ICD10_J45</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -6009,34 +6009,34 @@
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="6" t="n">
-        <v>0.999</v>
+        <v>0.667</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.879</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0.001</v>
+        <v>0.121</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>0.857</v>
+        <v>0.023</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>0.97</v>
+        <v>0.34</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>0.985</v>
+        <v>0.478</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>0.995</v>
+        <v>0.656</v>
       </c>
       <c r="M68" s="6" t="n">
         <v>0</v>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="P68" s="5" t="inlineStr">
         <is>
-          <t>ICD10_J80</t>
+          <t>ICD10_J62</t>
         </is>
       </c>
       <c r="Q68" s="5" t="inlineStr">
@@ -6069,35 +6069,35 @@
           <t>sage</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C69" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G69" s="5" t="n">
-        <v>0.993</v>
+      <c r="G69" s="6" t="n">
+        <v>0.898</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.007</v>
+        <v>0.102</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>0.332</v>
+        <v>0</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>0.802</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>0.896</v>
+        <v>0.254</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>0.964</v>
+        <v>0.601</v>
       </c>
       <c r="M69" s="6" t="n">
         <v>0</v>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="P69" s="5" t="inlineStr">
         <is>
-          <t>ICD10_J80</t>
+          <t>ICD10_J62</t>
         </is>
       </c>
       <c r="Q69" s="5" t="inlineStr">
@@ -6131,34 +6131,34 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>0.772</v>
+        <v>0.999</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.228</v>
+        <v>0.001</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>0.006</v>
+        <v>0.97</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0.06</v>
+        <v>0.985</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.337</v>
+        <v>0.995</v>
       </c>
       <c r="M70" s="4" t="n">
         <v>0</v>
@@ -6171,12 +6171,12 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>ICD10_K44</t>
+          <t>ICD10_J80</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the digestive system</t>
+          <t>Diseases of the respiratory system</t>
         </is>
       </c>
     </row>
@@ -6191,35 +6191,35 @@
           <t>sage</t>
         </is>
       </c>
-      <c r="C71" s="4" t="n">
+      <c r="C71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.672</v>
+        <v>0.993</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="I71" s="4" t="n">
-        <v>0</v>
+        <v>0.007</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>0.332</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.001</v>
+        <v>0.802</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.02</v>
+        <v>0.896</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0.232</v>
+        <v>0.964</v>
       </c>
       <c r="M71" s="4" t="n">
         <v>0</v>
@@ -6232,12 +6232,12 @@
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>ICD10_K44</t>
+          <t>ICD10_J80</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the digestive system</t>
+          <t>Diseases of the respiratory system</t>
         </is>
       </c>
     </row>
@@ -6256,31 +6256,31 @@
         <v>0</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>0.914</v>
+        <v>0.772</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.228</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>0.155</v>
+        <v>0</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>0.535</v>
+        <v>0.006</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>0.672</v>
+        <v>0.06</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>0.804</v>
+        <v>0.337</v>
       </c>
       <c r="M72" s="6" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="P72" s="5" t="inlineStr">
         <is>
-          <t>ICD10_K51</t>
+          <t>ICD10_K44</t>
         </is>
       </c>
       <c r="Q72" s="5" t="inlineStr">
@@ -6316,32 +6316,32 @@
       <c r="C73" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D73" s="5" t="n">
-        <v>0.25</v>
+      <c r="D73" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.897</v>
+        <v>0.672</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="I73" s="5" t="n">
-        <v>0.045</v>
+        <v>0.328</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>0.401</v>
+        <v>0.001</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>0.583</v>
+        <v>0.02</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0.766</v>
+        <v>0.232</v>
       </c>
       <c r="M73" s="6" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P73" s="5" t="inlineStr">
         <is>
-          <t>ICD10_K51</t>
+          <t>ICD10_K44</t>
         </is>
       </c>
       <c r="Q73" s="5" t="inlineStr">
@@ -6375,34 +6375,34 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>1</v>
+        <v>0.914</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.155</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>0.988</v>
+        <v>0.535</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0.994</v>
+        <v>0.672</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.998</v>
+        <v>0.804</v>
       </c>
       <c r="M74" s="4" t="n">
         <v>0</v>
@@ -6415,12 +6415,12 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>ICD10_L20</t>
+          <t>ICD10_K51</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the skin and subcutaneous tissue</t>
+          <t>Diseases of the digestive system</t>
         </is>
       </c>
     </row>
@@ -6436,34 +6436,34 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0.25</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.999</v>
+        <v>0.897</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.001</v>
+        <v>0.103</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.045</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.96</v>
+        <v>0.401</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.98</v>
+        <v>0.583</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.993</v>
+        <v>0.766</v>
       </c>
       <c r="M75" s="4" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>ICD10_L20</t>
+          <t>ICD10_K51</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the skin and subcutaneous tissue</t>
+          <t>Diseases of the digestive system</t>
         </is>
       </c>
     </row>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" s="6" t="n">
         <v>1</v>
@@ -6508,23 +6508,23 @@
       <c r="F76" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="5" t="n">
-        <v>0.946</v>
+      <c r="G76" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="I76" s="5" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J76" s="5" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="K76" s="5" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>0.752</v>
+        <v>0</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="K76" s="6" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="L76" s="6" t="n">
+        <v>0.998</v>
       </c>
       <c r="M76" s="6" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="P76" s="5" t="inlineStr">
         <is>
-          <t>ICD10_L40</t>
+          <t>ICD10_L20</t>
         </is>
       </c>
       <c r="Q76" s="5" t="inlineStr">
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="C77" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="6" t="n">
         <v>1</v>
@@ -6569,23 +6569,23 @@
       <c r="F77" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G77" s="6" t="n">
-        <v>0.957</v>
+      <c r="G77" s="5" t="n">
+        <v>0.999</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="I77" s="6" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="J77" s="6" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="K77" s="6" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="L77" s="6" t="n">
-        <v>0.798</v>
+        <v>0.001</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>0.993</v>
       </c>
       <c r="M77" s="6" t="n">
         <v>0</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="P77" s="5" t="inlineStr">
         <is>
-          <t>ICD10_L40</t>
+          <t>ICD10_L20</t>
         </is>
       </c>
       <c r="Q77" s="5" t="inlineStr">
@@ -6621,8 +6621,8 @@
       <c r="C78" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D78" s="3" t="n">
-        <v>0.5</v>
+      <c r="D78" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E78" s="4" t="n">
         <v>1</v>
@@ -6631,22 +6631,22 @@
         <v>1</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.985</v>
+        <v>0.946</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.015</v>
+        <v>0.054</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.231</v>
+        <v>0.001</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.645</v>
+        <v>0.198</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.793</v>
+        <v>0.432</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0.923</v>
+        <v>0.752</v>
       </c>
       <c r="M78" s="4" t="n">
         <v>0</v>
@@ -6659,12 +6659,12 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>ICD10_M32</t>
+          <t>ICD10_L40</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the musculoskeletal system and connective tissue</t>
+          <t>Diseases of the skin and subcutaneous tissue</t>
         </is>
       </c>
     </row>
@@ -6683,7 +6683,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>1</v>
@@ -6692,22 +6692,22 @@
         <v>1</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>0.989</v>
+        <v>0.957</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.012</v>
+        <v>0.043</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>0.289</v>
+        <v>0.004</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>0.713</v>
+        <v>0.273</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0.838</v>
+        <v>0.513</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.798</v>
       </c>
       <c r="M79" s="4" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>ICD10_M32</t>
+          <t>ICD10_L40</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
-          <t>Diseases of the musculoskeletal system and connective tissue</t>
+          <t>Diseases of the skin and subcutaneous tissue</t>
         </is>
       </c>
     </row>
@@ -6743,8 +6743,8 @@
       <c r="C80" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D80" s="6" t="n">
-        <v>1</v>
+      <c r="D80" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="E80" s="6" t="n">
         <v>1</v>
@@ -6752,23 +6752,23 @@
       <c r="F80" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G80" s="6" t="n">
-        <v>0.987</v>
+      <c r="G80" s="5" t="n">
+        <v>0.985</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="I80" s="6" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="J80" s="6" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="K80" s="6" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="L80" s="6" t="n">
-        <v>0.931</v>
+        <v>0.015</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>0.923</v>
       </c>
       <c r="M80" s="6" t="n">
         <v>0</v>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="P80" s="5" t="inlineStr">
         <is>
-          <t>ICD10_M34</t>
+          <t>ICD10_M32</t>
         </is>
       </c>
       <c r="Q80" s="5" t="inlineStr">
@@ -6804,8 +6804,8 @@
       <c r="C81" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D81" s="5" t="n">
-        <v>0</v>
+      <c r="D81" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="E81" s="6" t="n">
         <v>1</v>
@@ -6813,23 +6813,23 @@
       <c r="F81" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="5" t="n">
-        <v>0.972</v>
+      <c r="G81" s="6" t="n">
+        <v>0.989</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="K81" s="5" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>0.862</v>
+        <v>0.012</v>
+      </c>
+      <c r="I81" s="6" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="L81" s="6" t="n">
+        <v>0.9419999999999999</v>
       </c>
       <c r="M81" s="6" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P81" s="5" t="inlineStr">
         <is>
-          <t>ICD10_M34</t>
+          <t>ICD10_M32</t>
         </is>
       </c>
       <c r="Q81" s="5" t="inlineStr">
@@ -6866,31 +6866,31 @@
         <v>0</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>0.722</v>
+        <v>1</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0.987</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.278</v>
+        <v>0.014</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="3" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>0.238</v>
+        <v>0.115</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>0.931</v>
       </c>
       <c r="M82" s="4" t="n">
         <v>0</v>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>ICD10_M41</t>
+          <t>ICD10_M34</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -6926,32 +6926,32 @@
       <c r="C83" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D83" s="4" t="n">
+      <c r="D83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G83" s="4" t="n">
-        <v>0.744</v>
+        <v>1</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.972</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="I83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="4" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="K83" s="4" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="L83" s="4" t="n">
-        <v>0.343</v>
+        <v>0.028</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>0.862</v>
       </c>
       <c r="M83" s="4" t="n">
         <v>0</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>ICD10_M41</t>
+          <t>ICD10_M34</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -6987,32 +6987,32 @@
       <c r="C84" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D84" s="5" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="E84" s="5" t="n">
-        <v>0.667</v>
+      <c r="D84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.883</v>
+        <v>0.722</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="I84" s="5" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="5" t="n">
         <v>0.018</v>
       </c>
-      <c r="J84" s="5" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="K84" s="5" t="n">
-        <v>0.325</v>
-      </c>
       <c r="L84" s="5" t="n">
-        <v>0.595</v>
+        <v>0.238</v>
       </c>
       <c r="M84" s="6" t="n">
         <v>0</v>
@@ -7025,12 +7025,12 @@
       </c>
       <c r="P84" s="5" t="inlineStr">
         <is>
-          <t>ICD10_N04</t>
+          <t>ICD10_M41</t>
         </is>
       </c>
       <c r="Q84" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the genitourinary system</t>
+          <t>Diseases of the musculoskeletal system and connective tissue</t>
         </is>
       </c>
     </row>
@@ -7049,31 +7049,31 @@
         <v>0</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>0.968</v>
+        <v>0.744</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>0.032</v>
+        <v>0.256</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>0.52</v>
+        <v>0.018</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>0.668</v>
+        <v>0.095</v>
       </c>
       <c r="L85" s="6" t="n">
-        <v>0.854</v>
+        <v>0.343</v>
       </c>
       <c r="M85" s="6" t="n">
         <v>0</v>
@@ -7086,12 +7086,12 @@
       </c>
       <c r="P85" s="5" t="inlineStr">
         <is>
-          <t>ICD10_N04</t>
+          <t>ICD10_M41</t>
         </is>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>Diseases of the genitourinary system</t>
+          <t>Diseases of the musculoskeletal system and connective tissue</t>
         </is>
       </c>
     </row>
@@ -7109,32 +7109,32 @@
       <c r="C86" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>0</v>
+      <c r="D86" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.667</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.523</v>
+        <v>0.883</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.477</v>
-      </c>
-      <c r="I86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="4" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="K86" s="4" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="L86" s="4" t="n">
-        <v>0.188</v>
+        <v>0.117</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>0.595</v>
       </c>
       <c r="M86" s="4" t="n">
         <v>0</v>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>ICD10_N17</t>
+          <t>ICD10_N04</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -7171,31 +7171,31 @@
         <v>0</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>0.2</v>
+        <v>1</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>0.571</v>
+        <v>0.968</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.429</v>
+        <v>0.032</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>0.169</v>
+        <v>0.185</v>
+      </c>
+      <c r="J87" s="4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K87" s="4" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>0.854</v>
       </c>
       <c r="M87" s="4" t="n">
         <v>0</v>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>ICD10_N17</t>
+          <t>ICD10_N04</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -7232,31 +7232,31 @@
         <v>0</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="6" t="n">
-        <v>0.977</v>
+        <v>0.4</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.523</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="I88" s="5" t="n">
-        <v>0.043</v>
+        <v>0.477</v>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>0.493</v>
+        <v>0.007</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>0.698</v>
+        <v>0.042</v>
       </c>
       <c r="L88" s="6" t="n">
-        <v>0.887</v>
+        <v>0.188</v>
       </c>
       <c r="M88" s="6" t="n">
         <v>0</v>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="P88" s="5" t="inlineStr">
         <is>
-          <t>ICD10_N18</t>
+          <t>ICD10_N17</t>
         </is>
       </c>
       <c r="Q88" s="5" t="inlineStr">
@@ -7293,31 +7293,31 @@
         <v>0</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>0.95</v>
+        <v>0</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>0.571</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>0.05</v>
+        <v>0.429</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>0.346</v>
+        <v>0.002</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>0.522</v>
+        <v>0.023</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>0.779</v>
+        <v>0.169</v>
       </c>
       <c r="M89" s="6" t="n">
         <v>0</v>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P89" s="5" t="inlineStr">
         <is>
-          <t>ICD10_N18</t>
+          <t>ICD10_N17</t>
         </is>
       </c>
       <c r="Q89" s="5" t="inlineStr">
@@ -7354,31 +7354,31 @@
         <v>0</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0.555</v>
+        <v>1</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>0.977</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="I90" s="4" t="n">
-        <v>0</v>
+        <v>0.023</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0.043</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>0.188</v>
+        <v>0.493</v>
+      </c>
+      <c r="K90" s="4" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="L90" s="4" t="n">
+        <v>0.887</v>
       </c>
       <c r="M90" s="4" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>ICD10_N46</t>
+          <t>ICD10_N18</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -7415,31 +7415,31 @@
         <v>0</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>0.143</v>
+        <v>1</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="G91" s="4" t="n">
-        <v>0.613</v>
+        <v>1</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0.95</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.387</v>
+        <v>0.05</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K91" s="4" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="L91" s="4" t="n">
-        <v>0.249</v>
+        <v>0.346</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0.779</v>
       </c>
       <c r="M91" s="4" t="n">
         <v>0</v>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="P91" s="3" t="inlineStr">
         <is>
-          <t>ICD10_N46</t>
+          <t>ICD10_N18</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -7479,28 +7479,28 @@
         <v>0</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="6" t="n">
-        <v>0.715</v>
+        <v>0.143</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.555</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>0.285</v>
+        <v>0.445</v>
       </c>
       <c r="I92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L92" s="6" t="n">
-        <v>0.217</v>
+        <v>0.018</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>0.188</v>
       </c>
       <c r="M92" s="6" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="P92" s="5" t="inlineStr">
         <is>
-          <t>ICD10_N80</t>
+          <t>ICD10_N46</t>
         </is>
       </c>
       <c r="Q92" s="5" t="inlineStr">
@@ -7540,28 +7540,28 @@
         <v>0</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>0.497</v>
+        <v>0.143</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="G93" s="6" t="n">
+        <v>0.613</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0.503</v>
+        <v>0.387</v>
       </c>
       <c r="I93" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>0.065</v>
+      <c r="J93" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K93" s="6" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="L93" s="6" t="n">
+        <v>0.249</v>
       </c>
       <c r="M93" s="6" t="n">
         <v>0</v>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="P93" s="5" t="inlineStr">
         <is>
-          <t>ICD10_N80</t>
+          <t>ICD10_N46</t>
         </is>
       </c>
       <c r="Q93" s="5" t="inlineStr">
@@ -7597,32 +7597,32 @@
       <c r="C94" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="D94" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G94" s="3" t="n">
-        <v>0.954</v>
+      <c r="G94" s="4" t="n">
+        <v>0.715</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="K94" s="3" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>0.783</v>
+        <v>0.285</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L94" s="4" t="n">
+        <v>0.217</v>
       </c>
       <c r="M94" s="4" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>ICD10_N97</t>
+          <t>ICD10_N80</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -7659,47 +7659,169 @@
         <v>0</v>
       </c>
       <c r="D95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="I95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="M95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="3" t="inlineStr">
+        <is>
+          <t>ICD10_N80</t>
+        </is>
+      </c>
+      <c r="Q95" s="3" t="inlineStr">
+        <is>
+          <t>Diseases of the genitourinary system</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>random_negative</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>gcn</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="M96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="5" t="inlineStr">
+        <is>
+          <t>ICD10_N97</t>
+        </is>
+      </c>
+      <c r="Q96" s="5" t="inlineStr">
+        <is>
+          <t>Diseases of the genitourinary system</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>random_negative</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>sage</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="4" t="n">
+      <c r="E97" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="6" t="n">
         <v>0.978</v>
       </c>
-      <c r="H95" s="3" t="n">
+      <c r="H97" s="5" t="n">
         <v>0.022</v>
       </c>
-      <c r="I95" s="4" t="n">
+      <c r="I97" s="6" t="n">
         <v>0.179</v>
       </c>
-      <c r="J95" s="4" t="n">
+      <c r="J97" s="6" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K95" s="4" t="n">
+      <c r="K97" s="6" t="n">
         <v>0.728</v>
       </c>
-      <c r="L95" s="4" t="n">
+      <c r="L97" s="6" t="n">
         <v>0.894</v>
       </c>
-      <c r="M95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="3" t="inlineStr">
+      <c r="M97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="5" t="inlineStr">
         <is>
           <t>ICD10_N97</t>
         </is>
       </c>
-      <c r="Q95" s="3" t="inlineStr">
+      <c r="Q97" s="5" t="inlineStr">
         <is>
           <t>Diseases of the genitourinary system</t>
         </is>
